--- a/222/222_222/006_AKU11/条件输入数据表.xlsx
+++ b/222/222_222/006_AKU11/条件输入数据表.xlsx
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -1946,8 +1946,16 @@
           <t>MPa</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="25" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
           <t>工作温度（出口）</t>
@@ -2058,8 +2066,16 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="25" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
@@ -2134,8 +2150,16 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="25" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="inlineStr">
@@ -2506,8 +2530,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2568,7 +2592,7 @@
       <c r="C2" s="21" t="inlineStr"/>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2610,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2632,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>711</t>
         </is>
       </c>
     </row>
